--- a/artfynd/A 37723-2024 artfynd.xlsx
+++ b/artfynd/A 37723-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96474548</v>
+        <v>96474523</v>
       </c>
       <c r="B2" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,24 +686,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -716,13 +720,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537585.3998963704</v>
+        <v>537579</v>
       </c>
       <c r="R2" t="n">
-        <v>6702805.726839227</v>
+        <v>6702802</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -761,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,15 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96474523</v>
+        <v>96474548</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -804,33 +803,24 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>537578.5135733752</v>
+        <v>537585</v>
       </c>
       <c r="R3" t="n">
-        <v>6702802.695474974</v>
+        <v>6702806</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,7 +863,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -883,7 +873,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 37723-2024 artfynd.xlsx
+++ b/artfynd/A 37723-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96474523</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,8 +907,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96474548</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>